--- a/su25growr1.xlsx
+++ b/su25growr1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Kjuka_MasterThesis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oia08\Documents\GitHub\Kjuka_MasterThesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DFE27BF9-CD6F-43A0-8E2E-8BDB78835D75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6834EE0-30E5-4C3F-AAF9-D8926E8B249C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CBDEB34B-9D3E-4212-858D-ABE3C282FEA2}"/>
+    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15720" xr2:uid="{CBDEB34B-9D3E-4212-858D-ABE3C282FEA2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="70">
   <si>
     <t>Beetle</t>
   </si>
@@ -47,30 +47,6 @@
     <t>Plant_ID</t>
   </si>
   <si>
-    <t>R1</t>
-  </si>
-  <si>
-    <t>R2</t>
-  </si>
-  <si>
-    <t>R3</t>
-  </si>
-  <si>
-    <t>R4</t>
-  </si>
-  <si>
-    <t>R5</t>
-  </si>
-  <si>
-    <t>R6</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
     <t>C-Sb-1</t>
   </si>
   <si>
@@ -98,9 +74,6 @@
     <t>C-MBB-1</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
     <t>C-MBB-2</t>
   </si>
   <si>
@@ -161,9 +134,6 @@
     <t>C-Ex-5</t>
   </si>
   <si>
-    <t>MP</t>
-  </si>
-  <si>
     <t>MP-Sb-1</t>
   </si>
   <si>
@@ -249,6 +219,33 @@
   </si>
   <si>
     <t>MP-Ex-5</t>
+  </si>
+  <si>
+    <t>R_1</t>
+  </si>
+  <si>
+    <t>R_2</t>
+  </si>
+  <si>
+    <t>R_3</t>
+  </si>
+  <si>
+    <t>R_4</t>
+  </si>
+  <si>
+    <t>R_5</t>
+  </si>
+  <si>
+    <t>R_6</t>
+  </si>
+  <si>
+    <t>Control</t>
+  </si>
+  <si>
+    <t>Microplastic</t>
+  </si>
+  <si>
+    <t>No beetle</t>
   </si>
 </sst>
 </file>
@@ -635,9 +632,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0814EC93-D8B4-458D-A27E-051E39AFB547}">
   <dimension ref="A1:I59"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -648,33 +645,33 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
       </c>
       <c r="D2">
         <v>11</v>
@@ -695,15 +692,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D3">
         <v>11.5</v>
@@ -724,15 +721,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <v>10</v>
@@ -753,15 +750,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D5">
         <v>10.5</v>
@@ -782,15 +779,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D6">
         <v>10</v>
@@ -811,15 +808,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D7">
         <v>12</v>
@@ -840,15 +837,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" t="s">
         <v>9</v>
-      </c>
-      <c r="B8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" t="s">
-        <v>17</v>
       </c>
       <c r="D8">
         <v>11.5</v>
@@ -869,15 +866,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="B9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" t="s">
         <v>10</v>
-      </c>
-      <c r="C9" t="s">
-        <v>18</v>
       </c>
       <c r="D9">
         <v>12</v>
@@ -898,15 +895,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D10">
         <v>10</v>
@@ -927,15 +924,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -956,15 +953,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D12">
         <v>10.5</v>
@@ -985,15 +982,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D13">
         <v>11.5</v>
@@ -1014,15 +1011,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="B14" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D14">
         <v>11</v>
@@ -1043,15 +1040,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D15">
         <v>11</v>
@@ -1072,15 +1069,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="B16" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D16">
         <v>10</v>
@@ -1101,15 +1098,15 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="B17" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D17">
         <v>10</v>
@@ -1130,15 +1127,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="B18" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D18">
         <v>12</v>
@@ -1159,15 +1156,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="B19" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D19">
         <v>10</v>
@@ -1188,15 +1185,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="B20" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D20">
         <v>10</v>
@@ -1217,15 +1214,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="B21" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="C21" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D21">
         <v>11</v>
@@ -1246,15 +1243,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="B22" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="C22" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D22">
         <v>11</v>
@@ -1275,15 +1272,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="B23" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="C23" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D23">
         <v>11</v>
@@ -1304,15 +1301,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="B24" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="C24" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D24">
         <v>11</v>
@@ -1333,15 +1330,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="B25" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="C25" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D25">
         <v>11.5</v>
@@ -1362,15 +1359,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="B26" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="C26" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D26">
         <v>10</v>
@@ -1391,15 +1388,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="B27" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="C27" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D27">
         <v>9.5</v>
@@ -1420,15 +1417,15 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="B28" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="C28" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="D28">
         <v>9.5</v>
@@ -1449,15 +1446,15 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="B29" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="C29" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="D29">
         <v>10</v>
@@ -1478,15 +1475,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="B30" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="C30" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="D30">
         <v>10</v>
@@ -1507,15 +1504,15 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="B31" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="C31" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="D31">
         <v>10</v>
@@ -1536,15 +1533,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="C32" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="D32">
         <v>11.5</v>
@@ -1565,15 +1562,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="B33" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="C33" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D33">
         <v>10.5</v>
@@ -1594,15 +1591,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="B34" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="C34" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D34">
         <v>10</v>
@@ -1623,15 +1620,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="B35" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="C35" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D35">
         <v>10</v>
@@ -1652,15 +1649,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="B36" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="C36" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D36">
         <v>10</v>
@@ -1681,15 +1678,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="B37" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="C37" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="D37">
         <v>9.5</v>
@@ -1710,15 +1707,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="B38" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="C38" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="D38">
         <v>10</v>
@@ -1739,15 +1736,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="B39" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="C39" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D39">
         <v>11</v>
@@ -1768,15 +1765,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="B40" t="s">
+        <v>68</v>
+      </c>
+      <c r="C40" t="s">
         <v>41</v>
-      </c>
-      <c r="C40" t="s">
-        <v>51</v>
       </c>
       <c r="D40">
         <v>11</v>
@@ -1797,15 +1794,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="C41" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="D41">
         <v>11</v>
@@ -1826,15 +1823,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="B42" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="C42" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="D42">
         <v>11</v>
@@ -1855,15 +1852,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="B43" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="C43" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="D43">
         <v>11.5</v>
@@ -1884,15 +1881,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="B44" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="C44" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="D44">
         <v>11</v>
@@ -1913,15 +1910,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="B45" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="C45" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D45">
         <v>10.5</v>
@@ -1942,15 +1939,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="B46" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="C46" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="D46">
         <v>10</v>
@@ -1971,15 +1968,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="B47" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="C47" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="D47">
         <v>12</v>
@@ -2000,15 +1997,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="B48" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="C48" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="D48">
         <v>10</v>
@@ -2029,15 +2026,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="B49" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="C49" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D49">
         <v>11</v>
@@ -2058,15 +2055,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="B50" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="C50" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="D50">
         <v>10</v>
@@ -2087,15 +2084,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="B51" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="C51" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="D51">
         <v>10</v>
@@ -2116,15 +2113,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="B52" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="C52" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D52">
         <v>12</v>
@@ -2145,15 +2142,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="B53" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="C53" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D53">
         <v>10.5</v>
@@ -2174,15 +2171,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="B54" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="C54" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D54">
         <v>12</v>
@@ -2203,15 +2200,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="B55" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="C55" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="D55">
         <v>9.5</v>
@@ -2232,15 +2229,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="B56" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="C56" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D56">
         <v>10.5</v>
@@ -2261,15 +2258,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="B57" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="C57" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D57">
         <v>9.5</v>
@@ -2290,15 +2287,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="B58" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="C58" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D58">
         <v>10.5</v>
@@ -2319,15 +2316,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="B59" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="C59" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D59">
         <v>9.5</v>
@@ -2355,23 +2352,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="772c1424-85c2-441a-bfd7-8f15f1cf8684" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005B462E87CCDA0E4AB3F61CEBB8117501" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="81f3e62f49d47117f4e3bb445af46677">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="772c1424-85c2-441a-bfd7-8f15f1cf8684" xmlns:ns4="ced3a378-5222-455c-b98f-2fa57f9d5c74" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="23f0a3dd10f1dccac3bcaa5224c60a24" ns3:_="" ns4:_="">
     <xsd:import namespace="772c1424-85c2-441a-bfd7-8f15f1cf8684"/>
@@ -2604,25 +2584,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C19B4BB-15F2-413E-9C13-684746E5FC91}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="772c1424-85c2-441a-bfd7-8f15f1cf8684" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A029B27F-AAD8-48A4-93F5-6899F97CD893}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="772c1424-85c2-441a-bfd7-8f15f1cf8684"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA634382-6C8B-444B-A945-90A8756617A1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2641,6 +2620,24 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A029B27F-AAD8-48A4-93F5-6899F97CD893}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="772c1424-85c2-441a-bfd7-8f15f1cf8684"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C19B4BB-15F2-413E-9C13-684746E5FC91}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{a2761ec8-7198-4440-bea0-e9dd2af28b51}" enabled="1" method="Standard" siteId="{73e15cf5-5dbb-46af-a862-753916269d73}" removed="0"/>
